--- a/logicalfn.xlsx
+++ b/logicalfn.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Desktop\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D478F61-ABBC-43ED-9729-548CFFD9A67D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DBEB036-952E-4502-B8F9-18695B438354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{3AA7A386-516F-4153-A12A-D5FE31BB1D79}"/>
   </bookViews>
@@ -608,7 +608,7 @@
     <col min="9" max="9" width="16.21875" style="3" customWidth="1"/>
     <col min="10" max="10" width="16.5546875" customWidth="1"/>
     <col min="11" max="11" width="20.88671875" customWidth="1"/>
-    <col min="12" max="12" width="8.88671875" customWidth="1"/>
+    <col min="12" max="12" width="19.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
